--- a/pipeline/credit_rating/output/tmr_xhtn_20261029.xlsx
+++ b/pipeline/credit_rating/output/tmr_xhtn_20261029.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:53</t>
+          <t>2026-10-29 15:28:03</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:53</t>
+          <t>2026-10-29 15:28:03</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -687,7 +687,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:53</t>
+          <t>2026-10-29 15:28:03</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -748,7 +748,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:53</t>
+          <t>2026-10-29 15:28:03</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:53</t>
+          <t>2026-10-29 15:28:03</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:53</t>
+          <t>2026-10-29 15:28:03</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:53</t>
+          <t>2026-10-29 15:28:03</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:53</t>
+          <t>2026-10-29 15:28:03</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:53</t>
+          <t>2026-10-29 15:28:03</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:53</t>
+          <t>2026-10-29 15:28:03</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:53</t>
+          <t>2026-10-29 15:28:03</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:53</t>
+          <t>2026-10-29 15:28:03</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:53</t>
+          <t>2026-10-29 15:28:03</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:53</t>
+          <t>2026-10-29 15:28:03</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
